--- a/api/clv2/xlsx/fr/SectorVocabulary.xlsx
+++ b/api/clv2/xlsx/fr/SectorVocabulary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>code</t>
   </si>
@@ -91,7 +91,7 @@
     <t>Le secteur déclaré correspond à la taxonomie nationale des entités exonérées (NTEE) - États-Unis</t>
   </si>
   <si>
-    <t>http://nccs.urban.org/classification/NTEE.cfm</t>
+    <t>https://nccs.urban.org/publication/irs-activity-codes</t>
   </si>
   <si>
     <t>6</t>
@@ -112,7 +112,7 @@
     <t>Valeur tirée de la liste des principaux objectifs de développement durable (ODD) de l'ONU (p. ex. '1')</t>
   </si>
   <si>
-    <t>https://sustainabledevelopment.un.org/?menu=1300</t>
+    <t>http://reference.iatistandard.org/codelists/unsdg-goals</t>
   </si>
   <si>
     <t>8</t>
@@ -124,16 +124,19 @@
     <t>Valeur tirée de la liste des sous-objectifs de développement durable (ODD) de l'ONU (p. ex. '1.1')</t>
   </si>
   <si>
+    <t>http://reference.iatistandard.org/codelists/unsdg-targets</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ODD (indicateur)</t>
+  </si>
+  <si>
+    <t>Valeur tirée de la liste des indicateurs de développement durable (ODD) de deuxième niveau de l'ONU</t>
+  </si>
+  <si>
     <t>http://unstats.un.org/sdgs/indicators/indicators-list/</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>ODD (indicateur)</t>
-  </si>
-  <si>
-    <t>Valeur tirée de la liste des indicateurs de développement durable (ODD) de deuxième niveau de l'ONU</t>
   </si>
   <si>
     <t>10</t>
@@ -678,7 +681,7 @@
         <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -686,16 +689,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -703,10 +706,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -714,13 +717,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -728,13 +731,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
